--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487616_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487616_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.3403</v>
+        <v>5.758</v>
       </c>
       <c r="E2" t="n">
-        <v>5.3399</v>
+        <v>4.8394</v>
       </c>
       <c r="F2" t="n">
-        <v>1.0004</v>
+        <v>0.9187</v>
       </c>
       <c r="G2" t="n">
         <v>3.3526</v>
@@ -610,13 +610,13 @@
         <v>2.3284</v>
       </c>
       <c r="S2" t="n">
-        <v>1.122</v>
+        <v>0.5397999999999999</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6808</v>
+        <v>0.1803</v>
       </c>
       <c r="U2" t="n">
-        <v>0.4413</v>
+        <v>0.3595</v>
       </c>
       <c r="V2" t="n">
         <v>2.4477</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. VILA DE MIGUEL</t>
+          <t>P. ESTEBANEZ GONZALEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.0006</v>
+        <v>4.8985</v>
       </c>
       <c r="E3" t="n">
-        <v>2.093</v>
+        <v>3.7125</v>
       </c>
       <c r="F3" t="n">
-        <v>2.9076</v>
+        <v>1.186</v>
       </c>
       <c r="G3" t="n">
-        <v>1.1003</v>
+        <v>-0.7816</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7282999999999999</v>
+        <v>1.062</v>
       </c>
       <c r="I3" t="n">
-        <v>0.372</v>
+        <v>-1.8436</v>
       </c>
       <c r="J3" t="n">
-        <v>1.5457</v>
+        <v>0.8992</v>
       </c>
       <c r="K3" t="n">
-        <v>0.206</v>
+        <v>1.3635</v>
       </c>
       <c r="L3" t="n">
-        <v>1.3397</v>
+        <v>-0.4643</v>
       </c>
       <c r="M3" t="n">
-        <v>-0.4454</v>
+        <v>-1.6808</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5223</v>
+        <v>-0.3015</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.9677</v>
+        <v>-1.3792</v>
       </c>
       <c r="P3" t="n">
-        <v>1.9403</v>
+        <v>2.5224</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.9403</v>
+        <v>2.5224</v>
       </c>
       <c r="S3" t="n">
-        <v>1.5823</v>
+        <v>0.7099</v>
       </c>
       <c r="T3" t="n">
-        <v>0.5473</v>
+        <v>0.3656</v>
       </c>
       <c r="U3" t="n">
-        <v>1.035</v>
+        <v>0.3443</v>
       </c>
       <c r="V3" t="n">
-        <v>0.3776</v>
+        <v>2.4477</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>2.4477</v>
       </c>
       <c r="X3" t="n">
-        <v>0.3776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A. BIERSACK LOPEZ</t>
+          <t>P. VILA DE MIGUEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.5258</v>
+        <v>4.7008</v>
       </c>
       <c r="E4" t="n">
-        <v>3.603</v>
+        <v>2.093</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0772</v>
+        <v>2.6078</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.5325</v>
+        <v>1.1003</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.8819</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.6506</v>
+        <v>0.372</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.1613</v>
+        <v>1.5457</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.623</v>
+        <v>0.206</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4617</v>
+        <v>1.3397</v>
       </c>
       <c r="M4" t="n">
-        <v>-2.3712</v>
+        <v>-0.4454</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2589</v>
+        <v>0.5223</v>
       </c>
       <c r="O4" t="n">
-        <v>-1.1123</v>
+        <v>-0.9677</v>
       </c>
       <c r="P4" t="n">
-        <v>1.3582</v>
+        <v>1.9403</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3284</v>
+        <v>1.9403</v>
       </c>
       <c r="S4" t="n">
-        <v>2.6881</v>
+        <v>1.2825</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4405</v>
+        <v>0.5473</v>
       </c>
       <c r="U4" t="n">
-        <v>0.2477</v>
+        <v>0.7352</v>
       </c>
       <c r="V4" t="n">
-        <v>3.0119</v>
+        <v>0.3776</v>
       </c>
       <c r="W4" t="n">
-        <v>3.294</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2821</v>
+        <v>0.3776</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. ESTEBANEZ GONZALEZ</t>
+          <t>A. BIERSACK LOPEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>3.4248</v>
+        <v>2.5699</v>
       </c>
       <c r="E5" t="n">
-        <v>2.5113</v>
+        <v>2.4018</v>
       </c>
       <c r="F5" t="n">
-        <v>0.9134</v>
+        <v>0.1681</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.7816</v>
+        <v>-3.5325</v>
       </c>
       <c r="H5" t="n">
-        <v>1.062</v>
+        <v>-2.8819</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.8436</v>
+        <v>-0.6506</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8992</v>
+        <v>-1.1613</v>
       </c>
       <c r="K5" t="n">
-        <v>1.3635</v>
+        <v>-1.623</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.4643</v>
+        <v>0.4617</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.6808</v>
+        <v>-2.3712</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.3015</v>
+        <v>-1.2589</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.3792</v>
+        <v>-1.1123</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5224</v>
+        <v>1.3582</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R5" t="n">
-        <v>2.5224</v>
+        <v>2.3284</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7638</v>
+        <v>1.7322</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.8356</v>
+        <v>1.2393</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0718</v>
+        <v>0.493</v>
       </c>
       <c r="V5" t="n">
-        <v>2.4477</v>
+        <v>3.0119</v>
       </c>
       <c r="W5" t="n">
-        <v>2.4477</v>
+        <v>3.294</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.2821</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. VILLAMANDOS TORRES</t>
+          <t>A. GARCIA QUILEZ CUERVAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6954</v>
+        <v>0.4364</v>
       </c>
       <c r="E6" t="n">
-        <v>0.0071</v>
+        <v>1.5099</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6882</v>
+        <v>-1.0735</v>
       </c>
       <c r="G6" t="n">
-        <v>-2.9253</v>
+        <v>-0.6548</v>
       </c>
       <c r="H6" t="n">
-        <v>-2.6594</v>
+        <v>-0.7192</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.2659</v>
+        <v>0.0645</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.8441</v>
+        <v>1.0822</v>
       </c>
       <c r="K6" t="n">
-        <v>-2.2244</v>
+        <v>1.001</v>
       </c>
       <c r="L6" t="n">
-        <v>1.3803</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.0812</v>
+        <v>-1.737</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.435</v>
+        <v>-1.7202</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.6462</v>
+        <v>-0.0167</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9702</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.9403</v>
+        <v>0.5821</v>
       </c>
       <c r="S6" t="n">
-        <v>2.6505</v>
+        <v>-0.1029</v>
       </c>
       <c r="T6" t="n">
-        <v>1.8214</v>
+        <v>-0.1842</v>
       </c>
       <c r="U6" t="n">
-        <v>0.8290999999999999</v>
+        <v>0.0813</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>0.6119</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>P. ROSSI</t>
+          <t>O. HADI ADEGBITE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,40 +955,40 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.5654</v>
+        <v>0.08790000000000001</v>
       </c>
       <c r="E7" t="n">
-        <v>0.4728</v>
+        <v>-0.2166</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0927</v>
+        <v>0.3045</v>
       </c>
       <c r="G7" t="n">
-        <v>-3.3162</v>
+        <v>-0.9369</v>
       </c>
       <c r="H7" t="n">
-        <v>-2.9915</v>
+        <v>-0.8329</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.3248</v>
+        <v>-0.104</v>
       </c>
       <c r="J7" t="n">
-        <v>-2.4522</v>
+        <v>-0.2354</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.1987</v>
+        <v>-0.276</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.2535</v>
+        <v>0.0406</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.8641</v>
+        <v>-0.7015</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.7927</v>
+        <v>-0.5569</v>
       </c>
       <c r="O7" t="n">
-        <v>0.9287</v>
+        <v>-0.1446</v>
       </c>
       <c r="P7" t="n">
         <v>0.9702</v>
@@ -1000,28 +1000,28 @@
         <v>0.9702</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7458</v>
+        <v>-0.2274</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1951</v>
+        <v>-0.2633</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5507</v>
+        <v>0.0359</v>
       </c>
       <c r="V7" t="n">
-        <v>2.1657</v>
+        <v>0.2821</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7298</v>
+        <v>0.2821</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.5642</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A. GARCIA QUILEZ CUERVAS</t>
+          <t>P. ROSSI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.1088</v>
+        <v>0.0288</v>
       </c>
       <c r="E8" t="n">
-        <v>1.2096</v>
+        <v>0.07240000000000001</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.1008</v>
+        <v>-0.0436</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6548</v>
+        <v>-3.3162</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7192</v>
+        <v>-2.9915</v>
       </c>
       <c r="I8" t="n">
-        <v>0.0645</v>
+        <v>-0.3248</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0822</v>
+        <v>-2.4522</v>
       </c>
       <c r="K8" t="n">
-        <v>1.001</v>
+        <v>-1.1987</v>
       </c>
       <c r="L8" t="n">
-        <v>0.08119999999999999</v>
+        <v>-1.2535</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.737</v>
+        <v>-0.8641</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.7202</v>
+        <v>-1.7927</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0167</v>
+        <v>0.9287</v>
       </c>
       <c r="P8" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4305</v>
+        <v>0.2092</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4845</v>
+        <v>-0.2053</v>
       </c>
       <c r="U8" t="n">
-        <v>0.0541</v>
+        <v>0.4144</v>
       </c>
       <c r="V8" t="n">
-        <v>0.6119</v>
+        <v>2.1657</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6119</v>
+        <v>2.7298</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-0.5642</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>O. HADI ADEGBITE</t>
+          <t>S. PARADELA PARIS</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.0122</v>
+        <v>-0.161</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.3167</v>
+        <v>0.0014</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3045</v>
+        <v>-0.1625</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9369</v>
+        <v>-0.5584</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8329</v>
+        <v>-1.1328</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.104</v>
+        <v>0.5745</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.2354</v>
+        <v>0.1436</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.276</v>
+        <v>0.103</v>
       </c>
       <c r="L9" t="n">
         <v>0.0406</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.7015</v>
+        <v>-0.7019</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5569</v>
+        <v>-1.2358</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1446</v>
+        <v>0.5339</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="Q9" t="n">
         <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9702</v>
+        <v>0.5821</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.3275</v>
+        <v>-0.1848</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.3634</v>
+        <v>-0.1422</v>
       </c>
       <c r="U9" t="n">
-        <v>0.0359</v>
+        <v>-0.0426</v>
       </c>
       <c r="V9" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
         <v>0</v>
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.2875</v>
+        <v>-0.2329</v>
       </c>
       <c r="E10" t="n">
         <v>0.657</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.9445</v>
+        <v>-0.89</v>
       </c>
       <c r="G10" t="n">
         <v>1.5427</v>
@@ -1234,13 +1234,13 @@
         <v>0.3881</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0242</v>
+        <v>0.0303</v>
       </c>
       <c r="T10" t="n">
         <v>-0.0606</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V10" t="n">
         <v>-1.2239</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. PARADELA PARIS</t>
+          <t>M. VILLAMANDOS TORRES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,58 +1267,58 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.3157</v>
+        <v>-0.2506</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.0987</v>
+        <v>-0.6936</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.217</v>
+        <v>0.443</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.5584</v>
+        <v>-2.9253</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.1328</v>
+        <v>-2.6594</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5745</v>
+        <v>-0.2659</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1436</v>
+        <v>-0.8441</v>
       </c>
       <c r="K11" t="n">
-        <v>0.103</v>
+        <v>-2.2244</v>
       </c>
       <c r="L11" t="n">
-        <v>0.0406</v>
+        <v>1.3803</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.7019</v>
+        <v>-2.0812</v>
       </c>
       <c r="N11" t="n">
-        <v>-1.2358</v>
+        <v>-0.435</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5339</v>
+        <v>-1.6462</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5821</v>
+        <v>0.9702</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9702</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5821</v>
+        <v>1.9403</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3394</v>
+        <v>1.7045</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.2423</v>
+        <v>1.1207</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.09710000000000001</v>
+        <v>0.5838</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.5561</v>
+        <v>-1.5289</v>
       </c>
       <c r="E12" t="n">
         <v>0.0364</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.5925</v>
+        <v>-1.5652</v>
       </c>
       <c r="G12" t="n">
         <v>-0.9448</v>
@@ -1390,13 +1390,13 @@
         <v>0.5821</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0305</v>
+        <v>0.0578</v>
       </c>
       <c r="T12" t="n">
         <v>-0.0482</v>
       </c>
       <c r="U12" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.106</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2239</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-2.8612</v>
+        <v>-1.6783</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.0232</v>
+        <v>-0.9221</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.838</v>
+        <v>-0.7562</v>
       </c>
       <c r="G13" t="n">
         <v>-2.0185</v>
@@ -1468,13 +1468,13 @@
         <v>1.3582</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2607</v>
+        <v>0.9222</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.9085</v>
+        <v>0.1926</v>
       </c>
       <c r="U13" t="n">
-        <v>0.6478</v>
+        <v>0.7296</v>
       </c>
       <c r="V13" t="n">
         <v>0</v>
@@ -1501,16 +1501,16 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>14.6284</v>
+        <v>14.6286</v>
       </c>
       <c r="E14" t="n">
         <v>13.4915</v>
       </c>
       <c r="F14" t="n">
-        <v>1.1368</v>
+        <v>1.1371</v>
       </c>
       <c r="G14" t="n">
-        <v>-9.673399999999999</v>
+        <v>-9.673400000000001</v>
       </c>
       <c r="H14" t="n">
         <v>-8.254999999999999</v>
@@ -1534,10 +1534,10 @@
         <v>-11.1386</v>
       </c>
       <c r="O14" t="n">
-        <v>-4.9498</v>
+        <v>-4.949800000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>8.7315</v>
+        <v>8.731499999999999</v>
       </c>
       <c r="Q14" t="n">
         <v>-7.7614</v>
@@ -1546,13 +1546,13 @@
         <v>16.4928</v>
       </c>
       <c r="S14" t="n">
-        <v>6.673099999999999</v>
+        <v>6.673300000000001</v>
       </c>
       <c r="T14" t="n">
         <v>2.742</v>
       </c>
       <c r="U14" t="n">
-        <v>3.9313</v>
+        <v>3.9312</v>
       </c>
       <c r="V14" t="n">
         <v>8.896799999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8991</v>
+        <v>3.7633</v>
       </c>
       <c r="E15" t="n">
-        <v>2.5595</v>
+        <v>2.8598</v>
       </c>
       <c r="F15" t="n">
-        <v>1.3396</v>
+        <v>0.9036</v>
       </c>
       <c r="G15" t="n">
         <v>3.9183</v>
@@ -1624,13 +1624,13 @@
         <v>1.3582</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0013</v>
+        <v>-0.1371</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.8962</v>
+        <v>-0.5959</v>
       </c>
       <c r="U15" t="n">
-        <v>0.8948</v>
+        <v>0.4588</v>
       </c>
       <c r="V15" t="n">
         <v>0.5642</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
+          <t>I. MENCARA JIMENEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3011</v>
+        <v>1.2839</v>
       </c>
       <c r="E16" t="n">
-        <v>1.5645</v>
+        <v>3.6374</v>
       </c>
       <c r="F16" t="n">
-        <v>-0.2634</v>
+        <v>-2.3535</v>
       </c>
       <c r="G16" t="n">
-        <v>3.6481</v>
+        <v>4.5342</v>
       </c>
       <c r="H16" t="n">
-        <v>2.3307</v>
+        <v>1.7853</v>
       </c>
       <c r="I16" t="n">
-        <v>1.3174</v>
+        <v>2.7489</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4492</v>
+        <v>6.099</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3274</v>
+        <v>1.7095</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1218</v>
+        <v>4.3895</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1989</v>
+        <v>-1.5648</v>
       </c>
       <c r="N16" t="n">
-        <v>0.0033</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="O16" t="n">
-        <v>1.1956</v>
+        <v>-1.6406</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.1642</v>
+        <v>-1.9403</v>
       </c>
       <c r="Q16" t="n">
-        <v>-1.9403</v>
+        <v>-2.9105</v>
       </c>
       <c r="R16" t="n">
-        <v>0.7761</v>
+        <v>0.9702</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.5709</v>
+        <v>-1.31</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.1683</v>
+        <v>-0.775</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.4026</v>
+        <v>-0.535</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6119</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
         <v>1.2239</v>
       </c>
       <c r="X16" t="n">
-        <v>-1.8358</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>I. MENCARA JIMENEZ</t>
+          <t>A. REDONDO ALVAREZ DE SOTOMAYOR</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.9324</v>
+        <v>0.7282999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>3.6374</v>
+        <v>1.2642</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.705</v>
+        <v>-0.5359</v>
       </c>
       <c r="G17" t="n">
-        <v>4.5342</v>
+        <v>3.6481</v>
       </c>
       <c r="H17" t="n">
-        <v>1.7853</v>
+        <v>2.3307</v>
       </c>
       <c r="I17" t="n">
-        <v>2.7489</v>
+        <v>1.3174</v>
       </c>
       <c r="J17" t="n">
-        <v>6.099</v>
+        <v>2.4492</v>
       </c>
       <c r="K17" t="n">
-        <v>1.7095</v>
+        <v>2.3274</v>
       </c>
       <c r="L17" t="n">
-        <v>4.3895</v>
+        <v>0.1218</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.5648</v>
+        <v>1.1989</v>
       </c>
       <c r="N17" t="n">
-        <v>0.07580000000000001</v>
+        <v>0.0033</v>
       </c>
       <c r="O17" t="n">
-        <v>-1.6406</v>
+        <v>1.1956</v>
       </c>
       <c r="P17" t="n">
+        <v>-1.1642</v>
+      </c>
+      <c r="Q17" t="n">
         <v>-1.9403</v>
       </c>
-      <c r="Q17" t="n">
-        <v>-2.9105</v>
-      </c>
       <c r="R17" t="n">
-        <v>0.9702</v>
+        <v>0.7761</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.6615</v>
+        <v>-1.1437</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.775</v>
+        <v>-0.4686</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.8865</v>
+        <v>-0.6751</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6119</v>
       </c>
       <c r="W17" t="n">
         <v>1.2239</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.2239</v>
+        <v>-1.8358</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0707</v>
+        <v>-0.1614</v>
       </c>
       <c r="E18" t="n">
-        <v>2.4781</v>
+        <v>2.5782</v>
       </c>
       <c r="F18" t="n">
-        <v>-2.5488</v>
+        <v>-2.7396</v>
       </c>
       <c r="G18" t="n">
         <v>1.9317</v>
@@ -1858,13 +1858,13 @@
         <v>0.7761</v>
       </c>
       <c r="S18" t="n">
-        <v>0.3573</v>
+        <v>0.2667</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.2905</v>
+        <v>-0.1904</v>
       </c>
       <c r="U18" t="n">
-        <v>0.6478</v>
+        <v>0.4571</v>
       </c>
       <c r="V18" t="n">
         <v>-2.1657</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6832</v>
+        <v>-0.3195</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1453</v>
+        <v>0.0549</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.5379</v>
+        <v>-0.3744</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3436</v>
@@ -1936,13 +1936,13 @@
         <v>0.194</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.5336</v>
+        <v>-0.1699</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2423</v>
+        <v>-0.0421</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2914</v>
+        <v>-0.1278</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. SANTANA OJEDA</t>
+          <t>G. ARTILES ROMERO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6322</v>
+        <v>-1.5953</v>
       </c>
       <c r="E20" t="n">
-        <v>-2.6959</v>
+        <v>-0.7608</v>
       </c>
       <c r="F20" t="n">
-        <v>1.0638</v>
+        <v>-0.8345</v>
       </c>
       <c r="G20" t="n">
-        <v>0.4414</v>
+        <v>0.6122</v>
       </c>
       <c r="H20" t="n">
-        <v>0.8601</v>
+        <v>-0.8848</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.4187</v>
+        <v>1.497</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.2352</v>
+        <v>0.4081</v>
       </c>
       <c r="K20" t="n">
-        <v>1.1122</v>
+        <v>-0.9721</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3474</v>
+        <v>1.3803</v>
       </c>
       <c r="M20" t="n">
-        <v>0.6766</v>
+        <v>0.2041</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.2521</v>
+        <v>0.0873</v>
       </c>
       <c r="O20" t="n">
-        <v>0.9287</v>
+        <v>0.1168</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.1642</v>
+        <v>-0.5821</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.9403</v>
+        <v>-0.9702</v>
       </c>
       <c r="R20" t="n">
-        <v>0.7761</v>
+        <v>0.3881</v>
       </c>
       <c r="S20" t="n">
-        <v>0.3145</v>
+        <v>-1.0613</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5204</v>
+        <v>-0.4809</v>
       </c>
       <c r="U20" t="n">
-        <v>0.8349</v>
+        <v>-0.5804</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.2239</v>
+        <v>-0.5642</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>0.2821</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.2239</v>
+        <v>-0.8462</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>G. ARTILES ROMERO</t>
+          <t>A. SANTANA OJEDA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.0197</v>
+        <v>-1.65</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.8609</v>
+        <v>-2.4957</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.1588</v>
+        <v>0.8457</v>
       </c>
       <c r="G21" t="n">
-        <v>0.6122</v>
+        <v>0.4414</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.8848</v>
+        <v>0.8601</v>
       </c>
       <c r="I21" t="n">
-        <v>1.497</v>
+        <v>-0.4187</v>
       </c>
       <c r="J21" t="n">
-        <v>0.4081</v>
+        <v>-0.2352</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.9721</v>
+        <v>1.1122</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3803</v>
+        <v>-1.3474</v>
       </c>
       <c r="M21" t="n">
-        <v>0.2041</v>
+        <v>0.6766</v>
       </c>
       <c r="N21" t="n">
-        <v>0.0873</v>
+        <v>-0.2521</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1168</v>
+        <v>0.9287</v>
       </c>
       <c r="P21" t="n">
-        <v>-0.5821</v>
+        <v>-1.1642</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9702</v>
+        <v>-1.9403</v>
       </c>
       <c r="R21" t="n">
-        <v>0.3881</v>
+        <v>0.7761</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.4856</v>
+        <v>0.2967</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.581</v>
+        <v>-0.3202</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.9046</v>
+        <v>0.6169</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.5642</v>
+        <v>-1.2239</v>
       </c>
       <c r="W21" t="n">
-        <v>0.2821</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8462</v>
+        <v>-1.2239</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.254</v>
+        <v>-2.121</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.2205</v>
+        <v>-2.5208</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.0335</v>
+        <v>0.3998</v>
       </c>
       <c r="G22" t="n">
         <v>-1.3096</v>
@@ -2170,13 +2170,13 @@
         <v>1.1642</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.4787</v>
+        <v>-0.3457</v>
       </c>
       <c r="T22" t="n">
-        <v>0.1222</v>
+        <v>-0.1781</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.6009</v>
+        <v>-0.1677</v>
       </c>
       <c r="V22" t="n">
         <v>-0.6597</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.7978</v>
+        <v>-5.5097</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.1807</v>
+        <v>-1.0806</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.6171</v>
+        <v>-4.4292</v>
       </c>
       <c r="G23" t="n">
         <v>-0.4361</v>
@@ -2248,13 +2248,13 @@
         <v>0.5821</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.2737</v>
+        <v>-0.9856</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.581</v>
+        <v>-0.4809</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.6927</v>
+        <v>-0.5047</v>
       </c>
       <c r="V23" t="n">
         <v>-2.7298</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-8.3034</v>
+        <v>-8.3796</v>
       </c>
       <c r="E24" t="n">
-        <v>-4.273</v>
+        <v>-4.6734</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.0304</v>
+        <v>-3.7061</v>
       </c>
       <c r="G24" t="n">
         <v>-3.3233</v>
@@ -2326,13 +2326,13 @@
         <v>0.7761</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.3398</v>
+        <v>-1.416</v>
       </c>
       <c r="T24" t="n">
-        <v>0.0011</v>
+        <v>-0.3993</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.3409</v>
+        <v>-1.0167</v>
       </c>
       <c r="V24" t="n">
         <v>-1.506</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-14.6284</v>
+        <v>-13.961</v>
       </c>
       <c r="E25" t="n">
         <v>-1.1368</v>
       </c>
       <c r="F25" t="n">
-        <v>-13.4915</v>
+        <v>-12.8241</v>
       </c>
       <c r="G25" t="n">
         <v>9.673299999999999</v>
@@ -2374,7 +2374,7 @@
         <v>8.255099999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>1.4182</v>
+        <v>1.418199999999999</v>
       </c>
       <c r="J25" t="n">
         <v>16.0885</v>
@@ -2404,13 +2404,13 @@
         <v>7.761200000000001</v>
       </c>
       <c r="S25" t="n">
-        <v>-6.6733</v>
+        <v>-6.0059</v>
       </c>
       <c r="T25" t="n">
         <v>-3.9314</v>
       </c>
       <c r="U25" t="n">
-        <v>-2.7421</v>
+        <v>-2.0746</v>
       </c>
       <c r="V25" t="n">
         <v>-8.897</v>
